--- a/Digital Menu DD.xlsx
+++ b/Digital Menu DD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DD MENU pics video\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2D02EC-1288-4481-876F-C1931D03ED9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6932A2ED-59FF-478A-9F85-C2428E4C161F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1030,6 +1030,12 @@
       <c r="D6" s="4">
         <v>90</v>
       </c>
+      <c r="E6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1064,12 +1070,6 @@
       </c>
       <c r="D7" s="12">
         <v>110</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>17</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -30170,8 +30170,8 @@
     <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="E5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="E10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="F10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="E15" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
